--- a/backend/writable/products_master.xlsx
+++ b/backend/writable/products_master.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="175">
   <si>
     <t>id</t>
   </si>
@@ -552,61 +552,28 @@
     <t>1 year</t>
   </si>
   <si>
-    <t>aaaa</t>
-  </si>
-  <si>
-    <t>wer</t>
-  </si>
-  <si>
-    <t>1779170467_fc3b6681970e3739e3c4.webp</t>
-  </si>
-  <si>
-    <t>undefined</t>
-  </si>
-  <si>
-    <t>ddcdc</t>
-  </si>
-  <si>
-    <t>ccc</t>
+    <t>eee</t>
+  </si>
+  <si>
+    <t>ee</t>
+  </si>
+  <si>
+    <t>1779171342_c731392c1d6da2223625.webp</t>
+  </si>
+  <si>
+    <t>jj</t>
+  </si>
+  <si>
+    <t>n</t>
   </si>
   <si>
     <t>ddddd</t>
   </si>
   <si>
-    <t>ddd</t>
-  </si>
-  <si>
-    <t>1779170708_e697146fbf1f933d0909.jpg</t>
-  </si>
-  <si>
-    <t>gg</t>
-  </si>
-  <si>
-    <t>vv</t>
-  </si>
-  <si>
-    <t>ffff</t>
-  </si>
-  <si>
-    <t>1779171005_defb6ff8a05cb9ff032f.webp</t>
-  </si>
-  <si>
-    <t>vvvvv</t>
-  </si>
-  <si>
-    <t>eee</t>
-  </si>
-  <si>
-    <t>ee</t>
-  </si>
-  <si>
-    <t>1779171342_c731392c1d6da2223625.webp</t>
-  </si>
-  <si>
-    <t>jj</t>
-  </si>
-  <si>
-    <t>n</t>
+    <t>1779177577_7a58217a4d583d625043.webp</t>
+  </si>
+  <si>
+    <t>ff</t>
   </si>
 </sst>
 </file>
@@ -946,7 +913,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:AA24"/>
+  <dimension ref="A1:AA22"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" spans="1:27">
@@ -1912,13 +1879,13 @@
     </row>
     <row r="21" spans="1:27">
       <c r="A21">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B21" t="s">
         <v>167</v>
       </c>
       <c r="C21">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="D21" t="s">
         <v>168</v>
@@ -1930,148 +1897,66 @@
         <v>42</v>
       </c>
       <c r="G21">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H21">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="I21" t="s">
+        <v>51</v>
+      </c>
+      <c r="X21" t="s">
         <v>170</v>
       </c>
-      <c r="X21" t="s">
+      <c r="Y21" t="s">
         <v>171</v>
       </c>
-      <c r="Y21" t="s">
-        <v>172</v>
-      </c>
       <c r="Z21">
         <v>1</v>
       </c>
       <c r="AA21" t="s">
-        <v>46</v>
+        <v>167</v>
       </c>
     </row>
     <row r="22" spans="1:27">
       <c r="A22">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B22" t="s">
+        <v>172</v>
+      </c>
+      <c r="C22">
+        <v>11</v>
+      </c>
+      <c r="D22">
+        <v>11</v>
+      </c>
+      <c r="E22" t="s">
         <v>173</v>
-      </c>
-      <c r="C22">
-        <v>22</v>
-      </c>
-      <c r="D22" t="s">
-        <v>174</v>
-      </c>
-      <c r="E22" t="s">
-        <v>175</v>
       </c>
       <c r="F22" t="s">
         <v>42</v>
       </c>
       <c r="G22">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H22">
         <v>14</v>
       </c>
       <c r="I22" t="s">
-        <v>170</v>
+        <v>51</v>
       </c>
       <c r="X22" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="Y22" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="Z22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA22" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="23" spans="1:27">
-      <c r="A23">
-        <v>63</v>
-      </c>
-      <c r="B23" t="s">
-        <v>177</v>
-      </c>
-      <c r="C23">
-        <v>41</v>
-      </c>
-      <c r="D23" t="s">
-        <v>178</v>
-      </c>
-      <c r="E23" t="s">
-        <v>179</v>
-      </c>
-      <c r="F23" t="s">
-        <v>42</v>
-      </c>
-      <c r="G23">
-        <v>4</v>
-      </c>
-      <c r="H23">
-        <v>14</v>
-      </c>
-      <c r="I23" t="s">
-        <v>170</v>
-      </c>
-      <c r="X23" t="s">
-        <v>176</v>
-      </c>
-      <c r="Y23" t="s">
-        <v>176</v>
-      </c>
-      <c r="Z23">
-        <v>1</v>
-      </c>
-      <c r="AA23" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="24" spans="1:27">
-      <c r="A24">
-        <v>64</v>
-      </c>
-      <c r="B24" t="s">
-        <v>181</v>
-      </c>
-      <c r="C24">
-        <v>22</v>
-      </c>
-      <c r="D24" t="s">
-        <v>182</v>
-      </c>
-      <c r="E24" t="s">
-        <v>183</v>
-      </c>
-      <c r="F24" t="s">
-        <v>42</v>
-      </c>
-      <c r="G24">
-        <v>8</v>
-      </c>
-      <c r="H24">
-        <v>14</v>
-      </c>
-      <c r="I24" t="s">
-        <v>51</v>
-      </c>
-      <c r="X24" t="s">
-        <v>184</v>
-      </c>
-      <c r="Y24" t="s">
-        <v>185</v>
-      </c>
-      <c r="Z24">
-        <v>1</v>
-      </c>
-      <c r="AA24" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
     </row>
   </sheetData>
